--- a/artfynd/A 42574-2019 artfynd.xlsx
+++ b/artfynd/A 42574-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
